--- a/docs/uFerrisPinMapping.xlsx
+++ b/docs/uFerrisPinMapping.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10720"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10208"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/omarhiari/Documents/ErGitHub/uFerris-rs/docs/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/omarhiari/Documents/GitHub/uferris-hw/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B99AB4A-0262-6B47-AF19-8D46B20C8B08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2491260-6A8F-D948-9DD0-10641D17D52B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15960" yWindow="1000" windowWidth="28040" windowHeight="17080" xr2:uid="{FC8ADA73-E168-134B-9BF8-EF7089148C7F}"/>
+    <workbookView xWindow="46360" yWindow="2780" windowWidth="28040" windowHeight="17080" xr2:uid="{FC8ADA73-E168-134B-9BF8-EF7089148C7F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -356,9 +356,6 @@
     <t>LED</t>
   </si>
   <si>
-    <t>Case Label</t>
-  </si>
-  <si>
     <t>Snooze</t>
   </si>
   <si>
@@ -381,6 +378,9 @@
   </si>
   <si>
     <t>P15</t>
+  </si>
+  <si>
+    <t>Enclosure Label</t>
   </si>
 </sst>
 </file>
@@ -783,8 +783,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="34" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>106</v>
+      <c r="A1" s="3" t="s">
+        <v>114</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>2</v>
@@ -880,7 +880,7 @@
         <v>44</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>44</v>
@@ -929,7 +929,7 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>7</v>
@@ -958,7 +958,7 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>8</v>
@@ -987,7 +987,7 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>9</v>
@@ -1045,7 +1045,7 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>11</v>
@@ -1132,7 +1132,7 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>17</v>
@@ -1161,7 +1161,7 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>18</v>
@@ -1634,7 +1634,7 @@
         <v>90</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>81</v>
